--- a/artfynd/A 58205-2024 artfynd.xlsx
+++ b/artfynd/A 58205-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>91796214</v>
       </c>
       <c r="B2" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>457884.9582353801</v>
+        <v>457885</v>
       </c>
       <c r="R2" t="n">
-        <v>7044638.588899557</v>
+        <v>7044639</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -752,19 +747,9 @@
           <t>2017-05-26</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2017-05-26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -803,15 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>91796216</v>
+        <v>91796213</v>
       </c>
       <c r="B3" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -819,21 +799,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -847,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>457983.00248046</v>
+        <v>457807</v>
       </c>
       <c r="R3" t="n">
-        <v>7044788.119260441</v>
+        <v>7044688</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -880,19 +860,9 @@
           <t>2017-05-26</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2017-05-26</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -934,12 +904,7 @@
         <v>91796215</v>
       </c>
       <c r="B4" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -975,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>457876.4599251866</v>
+        <v>457876</v>
       </c>
       <c r="R4" t="n">
-        <v>7044671.723057041</v>
+        <v>7044672</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1008,19 +973,9 @@
           <t>2017-05-26</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2017-05-26</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1059,15 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>91796213</v>
+        <v>91796216</v>
       </c>
       <c r="B5" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,21 +1025,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1103,10 +1053,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>457806.5202594202</v>
+        <v>457983</v>
       </c>
       <c r="R5" t="n">
-        <v>7044687.821387491</v>
+        <v>7044788</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1136,19 +1086,9 @@
           <t>2017-05-26</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2017-05-26</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
